--- a/Config/Datas/revive_rule.xlsx
+++ b/Config/Datas/revive_rule.xlsx
@@ -758,7 +758,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>fallback_game_init</t>
+          <t>fallback_secretbase</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -771,17 +771,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FixedMap</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>game_init</t>
+          <t>SecretBase</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>BornPos</t>
+          <t>default</t>
         </is>
       </c>
       <c r="K7" t="b">
